--- a/HerculanoHouzel_etal_2015/HerculanoHouzel_etal_2015_Table1/HerculanoHouzel_etal_2015_Table1.xlsx
+++ b/HerculanoHouzel_etal_2015/HerculanoHouzel_etal_2015_Table1/HerculanoHouzel_etal_2015_Table1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/HerculanoHouzel_etal_2015/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo M1 Trait Data/HerculanoHouzel_etal_2015/HerculanoHouzel_etal_2015_Table1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{613DCA76-6844-DF41-B219-3AC6AAE2AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FA474B4-6754-3548-8E2D-518769F2A894}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{613DCA76-6844-DF41-B219-3AC6AAE2AC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{522058A1-E495-7E45-8B08-9B49345B12DF}"/>
   <bookViews>
-    <workbookView xWindow="37140" yWindow="-4640" windowWidth="26840" windowHeight="15940" xr2:uid="{56C7A9CD-3510-B74D-9A01-CDA80422F47C}"/>
+    <workbookView xWindow="36460" yWindow="-5860" windowWidth="29460" windowHeight="21300" xr2:uid="{56C7A9CD-3510-B74D-9A01-CDA80422F47C}"/>
   </bookViews>
   <sheets>
     <sheet name="publishedTable1cerebral cortex" sheetId="1" r:id="rId1"/>
@@ -2465,34 +2465,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
@@ -2503,8 +2488,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2820,1562 +2812,1224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D024C900-FC1E-EE44-848C-9A587F57583E}">
-  <dimension ref="A1:Q44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="6.33203125" defaultRowHeight="16"/>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="10" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" customWidth="1"/>
+    <col min="1" max="2" width="18" style="8" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="10" style="8" customWidth="1"/>
+    <col min="9" max="9" width="18" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="11.1640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20" customHeight="1">
+    <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="2"/>
+      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
+      <c r="I2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="16" customHeight="1">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:9" ht="16" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6" t="s">
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
     </row>
-    <row r="4" spans="1:17" ht="16" customHeight="1">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:9" ht="16" customHeight="1">
+      <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
+      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="G4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6" t="s">
+      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6" t="s">
+      <c r="I4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" ht="16" customHeight="1">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:9" ht="16" customHeight="1">
+      <c r="A5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
+      <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6" t="s">
+      <c r="F5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6" t="s">
+      <c r="G5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6" t="s">
+      <c r="H5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6" t="s">
+      <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" ht="16" customHeight="1">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:9" ht="16" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
+      <c r="F6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6" t="s">
+      <c r="G6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6" t="s">
+      <c r="H6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6" t="s">
+      <c r="I6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" ht="16" customHeight="1">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:9" ht="16" customHeight="1">
+      <c r="A7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="E7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6" t="s">
+      <c r="F7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6" t="s">
+      <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6" t="s">
+      <c r="H7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6" t="s">
+      <c r="I7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" ht="16" customHeight="1">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:9" ht="16" customHeight="1">
+      <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="s">
+      <c r="F8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6" t="s">
+      <c r="G8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6" t="s">
+      <c r="H8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6" t="s">
+      <c r="I8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" ht="16" customHeight="1">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:9" ht="16" customHeight="1">
+      <c r="A9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="E9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
+      <c r="F9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6" t="s">
+      <c r="G9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6" t="s">
+      <c r="H9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6" t="s">
+      <c r="I9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" ht="16" customHeight="1">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:9" ht="16" customHeight="1">
+      <c r="A10" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="E10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
+      <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6" t="s">
+      <c r="G10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6" t="s">
+      <c r="H10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6" t="s">
+      <c r="I10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" ht="16" customHeight="1">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:9" ht="16" customHeight="1">
+      <c r="A11" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="E11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
+      <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6" t="s">
+      <c r="G11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6" t="s">
+      <c r="H11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6" t="s">
+      <c r="I11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" ht="16" customHeight="1">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:9" ht="16" customHeight="1">
+      <c r="A12" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
+      <c r="E12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="s">
+      <c r="F12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6" t="s">
+      <c r="G12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6" t="s">
+      <c r="H12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6" t="s">
+      <c r="I12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" ht="16" customHeight="1">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:9" ht="16" customHeight="1">
+      <c r="A13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6" t="s">
+      <c r="E13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="s">
+      <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6" t="s">
+      <c r="G13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6" t="s">
+      <c r="H13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6" t="s">
+      <c r="I13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" ht="16" customHeight="1">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:9" ht="16" customHeight="1">
+      <c r="A14" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>0.90800000000000003</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8">
+      <c r="D14" s="4">
         <v>22310400</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="8">
+      <c r="E14" s="4">
         <v>70649600</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8">
+      <c r="F14" s="4">
         <v>24571</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="8">
+      <c r="G14" s="4">
         <v>77808</v>
       </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7">
+      <c r="H14" s="3">
         <v>3.1669999999999998</v>
       </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="6" t="s">
+      <c r="I14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="16" customHeight="1">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:9" ht="16" customHeight="1">
+      <c r="A15" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6" t="s">
+      <c r="E15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="s">
+      <c r="F15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6" t="s">
+      <c r="G15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6" t="s">
+      <c r="H15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6" t="s">
+      <c r="I15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" ht="16" customHeight="1">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:9" ht="16" customHeight="1">
+      <c r="A16" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6" t="s">
+      <c r="E16" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="s">
+      <c r="F16" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6" t="s">
+      <c r="G16" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6" t="s">
+      <c r="H16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6" t="s">
+      <c r="I16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="16" customHeight="1">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:9" ht="16" customHeight="1">
+      <c r="A17" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6" t="s">
+      <c r="E17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="s">
+      <c r="F17" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6" t="s">
+      <c r="G17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="7">
+      <c r="H17" s="3">
         <v>1.417</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6" t="s">
+      <c r="I17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" ht="16" customHeight="1">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:9" ht="16" customHeight="1">
+      <c r="A18" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6" t="s">
+      <c r="E18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="s">
+      <c r="F18" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6" t="s">
+      <c r="G18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6" t="s">
+      <c r="H18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6" t="s">
+      <c r="I18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" ht="16" customHeight="1">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:9" ht="16" customHeight="1">
+      <c r="A19" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6" t="s">
+      <c r="E19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="s">
+      <c r="F19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6" t="s">
+      <c r="G19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6" t="s">
+      <c r="H19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6" t="s">
+      <c r="I19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" ht="16" customHeight="1">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:9" ht="16" customHeight="1">
+      <c r="A20" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6" t="s">
+      <c r="E20" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
+      <c r="F20" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6" t="s">
+      <c r="G20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6" t="s">
+      <c r="H20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6" t="s">
+      <c r="I20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" ht="16" customHeight="1">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:9" ht="16" customHeight="1">
+      <c r="A21" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="3">
         <v>4.4480000000000004</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8">
+      <c r="D21" s="4">
         <v>71448750</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8">
+      <c r="E21" s="4">
         <v>254801250</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="8">
+      <c r="F21" s="4">
         <v>16063</v>
       </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="8">
+      <c r="G21" s="4">
         <v>57284</v>
       </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7">
+      <c r="H21" s="3">
         <v>3.5659999999999998</v>
       </c>
-      <c r="N21" s="7"/>
-      <c r="O21" s="6" t="s">
+      <c r="I21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" ht="16" customHeight="1">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:9" ht="16" customHeight="1">
+      <c r="A22" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6" t="s">
+      <c r="E22" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6" t="s">
+      <c r="F22" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6" t="s">
+      <c r="G22" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="7">
+      <c r="H22" s="3">
         <v>1.615</v>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6" t="s">
+      <c r="I22" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" ht="16" customHeight="1">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:9" ht="16" customHeight="1">
+      <c r="A23" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6" t="s">
+      <c r="E23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6" t="s">
+      <c r="F23" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6" t="s">
+      <c r="G23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="7">
+      <c r="H23" s="3">
         <v>1.778</v>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6" t="s">
+      <c r="I23" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" ht="16" customHeight="1">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:9" ht="16" customHeight="1">
+      <c r="A24" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="5">
         <v>7.56</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="8">
+      <c r="D24" s="4">
         <v>98960000</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="8">
+      <c r="E24" s="4">
         <v>183540000</v>
       </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="8">
+      <c r="F24" s="4">
         <v>13098</v>
       </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="8">
+      <c r="G24" s="4">
         <v>24291</v>
       </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="7">
+      <c r="H24" s="3">
         <v>1.855</v>
       </c>
-      <c r="N24" s="10"/>
-      <c r="O24" s="6" t="s">
+      <c r="I24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="16" customHeight="1">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:9" ht="16" customHeight="1">
+      <c r="A25" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6" t="s">
+      <c r="E25" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6" t="s">
+      <c r="F25" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6" t="s">
+      <c r="G25" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6" t="s">
+      <c r="H25" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6" t="s">
+      <c r="I25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" ht="16" customHeight="1">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:9" ht="16" customHeight="1">
+      <c r="A26" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6" t="s">
+      <c r="E26" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6" t="s">
+      <c r="F26" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6" t="s">
+      <c r="G26" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6" t="s">
+      <c r="H26" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6" t="s">
+      <c r="I26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" ht="16" customHeight="1">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:9" ht="16" customHeight="1">
+      <c r="A27" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6" t="s">
+      <c r="E27" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6" t="s">
+      <c r="F27" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6" t="s">
+      <c r="G27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="7">
+      <c r="H27" s="3">
         <v>1.5740000000000001</v>
       </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6" t="s">
+      <c r="I27" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
     </row>
-    <row r="28" spans="1:17" ht="16" customHeight="1">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:9" ht="16" customHeight="1">
+      <c r="A28" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="3">
         <v>12.984</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8">
+      <c r="D28" s="4">
         <v>357129180</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8">
+      <c r="E28" s="4">
         <v>715330820</v>
       </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="8">
+      <c r="F28" s="4">
         <v>27505</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="8">
+      <c r="G28" s="4">
         <v>55093</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7">
+      <c r="H28" s="3">
         <v>2.0030000000000001</v>
       </c>
-      <c r="N28" s="7"/>
-      <c r="O28" s="6" t="s">
+      <c r="I28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" ht="16" customHeight="1">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:9" ht="16" customHeight="1">
+      <c r="A29" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6" t="s">
+      <c r="E29" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6" t="s">
+      <c r="F29" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6" t="s">
+      <c r="G29" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7">
+      <c r="H29" s="3">
         <v>1.2010000000000001</v>
       </c>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6" t="s">
+      <c r="I29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" ht="16" customHeight="1">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:9" ht="16" customHeight="1">
+      <c r="A30" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="3">
         <v>36.225999999999999</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8">
+      <c r="D30" s="4">
         <v>800955000</v>
       </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="8">
+      <c r="E30" s="4">
         <v>2758845000</v>
       </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="8">
+      <c r="F30" s="4">
         <v>22110</v>
       </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="8">
+      <c r="G30" s="4">
         <v>76156</v>
       </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7">
+      <c r="H30" s="3">
         <v>3.444</v>
       </c>
-      <c r="N30" s="7"/>
-      <c r="O30" s="6" t="s">
+      <c r="I30" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" ht="16" customHeight="1">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:9" ht="16" customHeight="1">
+      <c r="A31" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="3">
         <v>39.177999999999997</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="8">
+      <c r="D31" s="4">
         <v>1140000000</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8">
+      <c r="E31" s="4">
         <v>2550000000</v>
       </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="8">
+      <c r="F31" s="4">
         <v>29180</v>
       </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="8">
+      <c r="G31" s="4">
         <v>64980</v>
       </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7">
+      <c r="H31" s="3">
         <v>2.2370000000000001</v>
       </c>
-      <c r="N31" s="7"/>
-      <c r="O31" s="6" t="s">
+      <c r="I31" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" ht="16" customHeight="1">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:9" ht="16" customHeight="1">
+      <c r="A32" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="3">
         <v>48.274000000000001</v>
       </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="8">
+      <c r="D32" s="4">
         <v>1655707140</v>
       </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8">
+      <c r="E32" s="4">
         <v>3808672860</v>
       </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="8">
+      <c r="F32" s="4">
         <v>34298</v>
       </c>
-      <c r="J32" s="7"/>
-      <c r="K32" s="8">
+      <c r="G32" s="4">
         <v>78897</v>
       </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7">
+      <c r="H32" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="N32" s="7"/>
-      <c r="O32" s="6" t="s">
+      <c r="I32" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" ht="16" customHeight="1">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:9" ht="16" customHeight="1">
+      <c r="A33" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="3">
         <v>42.404000000000003</v>
       </c>
-      <c r="D33" s="7"/>
-      <c r="E33" s="8">
+      <c r="D33" s="4">
         <v>307082404</v>
       </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="8">
+      <c r="E33" s="4">
         <v>3250251354</v>
       </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="8">
+      <c r="F33" s="4">
         <v>7276</v>
       </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="8">
+      <c r="G33" s="4">
         <v>77016</v>
       </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7">
+      <c r="H33" s="3">
         <v>10.585000000000001</v>
       </c>
-      <c r="N33" s="7"/>
-      <c r="O33" s="6" t="s">
+      <c r="I33" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" ht="16" customHeight="1">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:9" ht="16" customHeight="1">
+      <c r="A34" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6" t="s">
+      <c r="E34" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6" t="s">
+      <c r="F34" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6" t="s">
+      <c r="G34" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6" t="s">
+      <c r="H34" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6" t="s">
+      <c r="I34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" ht="16" customHeight="1">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:9" ht="16" customHeight="1">
+      <c r="A35" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="3">
         <v>68.805999999999997</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="8">
+      <c r="D35" s="4">
         <v>396896159</v>
       </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="8">
+      <c r="E35" s="4">
         <v>4126259275</v>
       </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="8">
+      <c r="F35" s="4">
         <v>5768</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="8">
+      <c r="G35" s="4">
         <v>59969</v>
       </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7">
+      <c r="H35" s="3">
         <v>10.396000000000001</v>
       </c>
-      <c r="N35" s="7"/>
-      <c r="O35" s="6" t="s">
+      <c r="I35" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" ht="16" customHeight="1">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:9" ht="16" customHeight="1">
+      <c r="A36" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="3">
         <v>69.831999999999994</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="8">
+      <c r="D36" s="4">
         <v>1710000000</v>
       </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="8">
+      <c r="E36" s="4">
         <v>5270000000</v>
       </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="8">
+      <c r="F36" s="4">
         <v>24470</v>
       </c>
-      <c r="J36" s="7"/>
-      <c r="K36" s="8">
+      <c r="G36" s="4">
         <v>75400</v>
       </c>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7">
+      <c r="H36" s="3">
         <v>3.0819999999999999</v>
       </c>
-      <c r="N36" s="7"/>
-      <c r="O36" s="6" t="s">
+      <c r="I36" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" ht="16" customHeight="1">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:9" ht="16" customHeight="1">
+      <c r="A37" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="3">
         <v>111.31</v>
       </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="8">
+      <c r="D37" s="4">
         <v>570673431</v>
       </c>
-      <c r="F37" s="7"/>
-      <c r="G37" s="8">
+      <c r="E37" s="4">
         <v>6762256227</v>
       </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="8">
+      <c r="F37" s="4">
         <v>5127</v>
       </c>
-      <c r="J37" s="7"/>
-      <c r="K37" s="8">
+      <c r="G37" s="4">
         <v>60760</v>
       </c>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7">
+      <c r="H37" s="3">
         <v>11.851000000000001</v>
       </c>
-      <c r="N37" s="7"/>
-      <c r="O37" s="6" t="s">
+      <c r="I37" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="16" customHeight="1">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:9" ht="16" customHeight="1">
+      <c r="A38" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="3">
         <v>120.214</v>
       </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8">
+      <c r="D38" s="4">
         <v>2875028372</v>
       </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="8">
+      <c r="E38" s="4">
         <v>7569751628</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="8">
+      <c r="F38" s="4">
         <v>23916</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="8">
+      <c r="G38" s="4">
         <v>62969</v>
       </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7">
+      <c r="H38" s="3">
         <v>2.633</v>
       </c>
-      <c r="N38" s="7"/>
-      <c r="O38" s="6" t="s">
+      <c r="I38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" ht="16" customHeight="1">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:9" ht="16" customHeight="1">
+      <c r="A39" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="3">
         <v>213.37</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="8">
+      <c r="D39" s="4">
         <v>762567178</v>
       </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8">
+      <c r="E39" s="4">
         <v>12302304448</v>
       </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="8">
+      <c r="F39" s="4">
         <v>3574</v>
       </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="8">
+      <c r="G39" s="4">
         <v>57657</v>
       </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7">
+      <c r="H39" s="3">
         <v>16.132999999999999</v>
       </c>
-      <c r="N39" s="7"/>
-      <c r="O39" s="6" t="s">
+      <c r="I39" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="16" customHeight="1">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:9" ht="16" customHeight="1">
+      <c r="A40" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="3">
         <v>398.80799999999999</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="8">
+      <c r="D40" s="4">
         <v>1730513460</v>
       </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="8">
+      <c r="E40" s="4">
         <v>27513706540</v>
       </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="8">
+      <c r="F40" s="4">
         <v>4339</v>
       </c>
-      <c r="J40" s="7"/>
-      <c r="K40" s="8">
+      <c r="G40" s="4">
         <v>68990</v>
       </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7">
+      <c r="H40" s="3">
         <v>15.9</v>
       </c>
-      <c r="N40" s="7"/>
-      <c r="O40" s="6" t="s">
+      <c r="I40" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="16" customHeight="1">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:9" ht="16" customHeight="1">
+      <c r="A41" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6" t="s">
+      <c r="D41" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6" t="s">
+      <c r="E41" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6" t="s">
+      <c r="F41" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6" t="s">
+      <c r="G41" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6" t="s">
+      <c r="H41" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6" t="s">
+      <c r="I41" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="16" customHeight="1">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:9" ht="16" customHeight="1">
+      <c r="A42" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="6">
         <v>2847.5940000000001</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="8">
+      <c r="D42" s="4">
         <v>5593241033</v>
       </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="8">
+      <c r="E42" s="4">
         <v>55698998687</v>
       </c>
-      <c r="H42" s="11"/>
-      <c r="I42" s="8">
+      <c r="F42" s="4">
         <v>1964</v>
       </c>
-      <c r="J42" s="11"/>
-      <c r="K42" s="8">
+      <c r="G42" s="4">
         <v>52721</v>
       </c>
-      <c r="L42" s="11"/>
-      <c r="M42" s="7">
+      <c r="H42" s="3">
         <v>26.844000000000001</v>
       </c>
-      <c r="N42" s="11"/>
-      <c r="O42" s="6" t="s">
+      <c r="I42" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
     </row>
-    <row r="44" spans="1:17">
-      <c r="A44" s="12" t="s">
+    <row r="44" spans="1:9">
+      <c r="A44" s="7" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4385,15 +4039,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acb3cbe4b9dee1876b3bbe7116f679b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca927c27970307cd175704f09b582c5c" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -4630,6 +4275,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4642,14 +4296,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0050517-C7FB-4C07-8D4F-03C10DF9C2EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCDB4A4A-F196-4994-BB0E-AF8E282DF1DD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4668,19 +4314,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0050517-C7FB-4C07-8D4F-03C10DF9C2EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC62E09E-5D24-4CFF-A30F-B1D70B65D56E}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>